--- a/Assets/Resources/DataFiles/SkillData/ExcelFile/SkillDataLabel.xlsx
+++ b/Assets/Resources/DataFiles/SkillData/ExcelFile/SkillDataLabel.xlsx
@@ -608,7 +608,11 @@
           <t>스택 1개로 약화된 투사체(피해 50%)를 0.1초 간격으로 3발 연속 발사합니다. 폭발하지 않고 명중한 대상 하나에게만 피해를 줍니다.</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>스택을 2개 소모해 폭발 반경이 3(기본의 3배)으로 크게 늘어난 확장 폭발탄을 발사합니다. 피해 배율도 250%로 크게 증가합니다.</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>피해량이 55% 증가합니다.</t>
